--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G537"/>
+  <dimension ref="A1:G538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14935,6 +14935,33 @@
         <v>395.81</v>
       </c>
       <c r="G537" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>375.22</v>
+      </c>
+      <c r="C538" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="D538" t="n">
+        <v>391.17</v>
+      </c>
+      <c r="E538" t="n">
+        <v>393.12</v>
+      </c>
+      <c r="F538" t="n">
+        <v>395.56</v>
+      </c>
+      <c r="G538" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -14951,7 +14978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B614"/>
+  <dimension ref="A1:B615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21094,6 +21121,16 @@
       </c>
       <c r="B614" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -21262,28 +21299,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1762277302990946</v>
+        <v>0.1735298552112953</v>
       </c>
       <c r="J2" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K2" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L2" t="n">
-        <v>0.12753510495594</v>
+        <v>0.1235372588251444</v>
       </c>
       <c r="M2" t="n">
-        <v>2.727275793021985</v>
+        <v>2.735822891453412</v>
       </c>
       <c r="N2" t="n">
-        <v>12.44010125473681</v>
+        <v>12.53240708664634</v>
       </c>
       <c r="O2" t="n">
-        <v>3.527052771753892</v>
+        <v>3.540113993453649</v>
       </c>
       <c r="P2" t="n">
-        <v>378.4834394263084</v>
+        <v>378.5105488156653</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21340,28 +21377,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2336870336451437</v>
+        <v>0.2312273846240813</v>
       </c>
       <c r="J3" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K3" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2338392056660958</v>
+        <v>0.2291059655195616</v>
       </c>
       <c r="M3" t="n">
-        <v>2.633043777926482</v>
+        <v>2.641564455572729</v>
       </c>
       <c r="N3" t="n">
-        <v>10.47680911492028</v>
+        <v>10.55327870431269</v>
       </c>
       <c r="O3" t="n">
-        <v>3.236789939881838</v>
+        <v>3.248581029359232</v>
       </c>
       <c r="P3" t="n">
-        <v>381.3631167749098</v>
+        <v>381.3878323680427</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21418,28 +21455,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04279540432158681</v>
+        <v>0.0417124415247122</v>
       </c>
       <c r="J4" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K4" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01285507729758006</v>
+        <v>0.01223781887802289</v>
       </c>
       <c r="M4" t="n">
-        <v>2.218252529626781</v>
+        <v>2.220380880395096</v>
       </c>
       <c r="N4" t="n">
-        <v>8.234887935432052</v>
+        <v>8.238159212198438</v>
       </c>
       <c r="O4" t="n">
-        <v>2.869649444693908</v>
+        <v>2.870219366563894</v>
       </c>
       <c r="P4" t="n">
-        <v>393.2197777536045</v>
+        <v>393.2306598215891</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21496,28 +21533,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03399884997051975</v>
+        <v>-0.03560885711051515</v>
       </c>
       <c r="J5" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K5" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00827102719106243</v>
+        <v>0.009053323551854953</v>
       </c>
       <c r="M5" t="n">
-        <v>2.299218102603345</v>
+        <v>2.303811151626612</v>
       </c>
       <c r="N5" t="n">
-        <v>8.115573374459913</v>
+        <v>8.141583850327656</v>
       </c>
       <c r="O5" t="n">
-        <v>2.848784543355273</v>
+        <v>2.853346079662903</v>
       </c>
       <c r="P5" t="n">
-        <v>398.7278144014384</v>
+        <v>398.7439924337805</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21574,28 +21611,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2709001122369487</v>
+        <v>-0.2726864014238115</v>
       </c>
       <c r="J6" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K6" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07189471163328887</v>
+        <v>0.07296435188738981</v>
       </c>
       <c r="M6" t="n">
-        <v>5.869415439295662</v>
+        <v>5.866065226698774</v>
       </c>
       <c r="N6" t="n">
-        <v>55.47226169738492</v>
+        <v>55.41958296892471</v>
       </c>
       <c r="O6" t="n">
-        <v>7.447970307230348</v>
+        <v>7.444433018633771</v>
       </c>
       <c r="P6" t="n">
-        <v>407.8979960971012</v>
+        <v>407.9159454859701</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21633,7 +21670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G537"/>
+  <dimension ref="A1:G538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41505,6 +41542,43 @@
         </is>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-35.01265214340639,173.8525843540029</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-35.01305551279979,173.85330281739763</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-35.01327718301313,173.8541401675355</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-35.01353407400494,173.854879708965</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-35.01344381220291,173.85567710096896</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G538"/>
+  <dimension ref="A1:G541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14964,6 +14964,87 @@
       <c r="G538" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>375.49</v>
+      </c>
+      <c r="C539" t="n">
+        <v>380.27</v>
+      </c>
+      <c r="D539" t="n">
+        <v>390.54</v>
+      </c>
+      <c r="E539" t="n">
+        <v>392.65</v>
+      </c>
+      <c r="F539" t="n">
+        <v>396.68</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>375.76</v>
+      </c>
+      <c r="C540" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="D540" t="n">
+        <v>390.56</v>
+      </c>
+      <c r="E540" t="n">
+        <v>393.18</v>
+      </c>
+      <c r="F540" t="n">
+        <v>397.59</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>374.37</v>
+      </c>
+      <c r="C541" t="n">
+        <v>379.27</v>
+      </c>
+      <c r="D541" t="n">
+        <v>389.51</v>
+      </c>
+      <c r="E541" t="n">
+        <v>392.2</v>
+      </c>
+      <c r="F541" t="n">
+        <v>396.03</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14978,7 +15059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B615"/>
+  <dimension ref="A1:B618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21131,6 +21212,36 @@
       </c>
       <c r="B615" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -21299,28 +21410,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1735298552112953</v>
+        <v>0.16555759085466</v>
       </c>
       <c r="J2" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="K2" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1235372588251444</v>
+        <v>0.1121122705547676</v>
       </c>
       <c r="M2" t="n">
-        <v>2.735822891453412</v>
+        <v>2.760866761042239</v>
       </c>
       <c r="N2" t="n">
-        <v>12.53240708664634</v>
+        <v>12.80318917506866</v>
       </c>
       <c r="O2" t="n">
-        <v>3.540113993453649</v>
+        <v>3.57815443700641</v>
       </c>
       <c r="P2" t="n">
-        <v>378.5105488156653</v>
+        <v>378.590869402714</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21377,28 +21488,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2312273846240813</v>
+        <v>0.2236478662760924</v>
       </c>
       <c r="J3" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="K3" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2291059655195616</v>
+        <v>0.2145226629122596</v>
       </c>
       <c r="M3" t="n">
-        <v>2.641564455572729</v>
+        <v>2.669573813277388</v>
       </c>
       <c r="N3" t="n">
-        <v>10.55327870431269</v>
+        <v>10.80202202755234</v>
       </c>
       <c r="O3" t="n">
-        <v>3.248581029359232</v>
+        <v>3.286642972327896</v>
       </c>
       <c r="P3" t="n">
-        <v>381.3878323680427</v>
+        <v>381.4641958199472</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21455,28 +21566,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0417124415247122</v>
+        <v>0.03753634809745329</v>
       </c>
       <c r="J4" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="K4" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01223781887802289</v>
+        <v>0.009929114832593733</v>
       </c>
       <c r="M4" t="n">
-        <v>2.220380880395096</v>
+        <v>2.232058202294005</v>
       </c>
       <c r="N4" t="n">
-        <v>8.238159212198438</v>
+        <v>8.286570935819514</v>
       </c>
       <c r="O4" t="n">
-        <v>2.870219366563894</v>
+        <v>2.878640466577845</v>
       </c>
       <c r="P4" t="n">
-        <v>393.2306598215891</v>
+        <v>393.2727349051239</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21533,28 +21644,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03560885711051515</v>
+        <v>-0.04080745370151635</v>
       </c>
       <c r="J5" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="K5" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009053323551854953</v>
+        <v>0.01177772133284005</v>
       </c>
       <c r="M5" t="n">
-        <v>2.303811151626612</v>
+        <v>2.319733521613529</v>
       </c>
       <c r="N5" t="n">
-        <v>8.141583850327656</v>
+        <v>8.241142422964277</v>
       </c>
       <c r="O5" t="n">
-        <v>2.853346079662903</v>
+        <v>2.870739002933613</v>
       </c>
       <c r="P5" t="n">
-        <v>398.7439924337805</v>
+        <v>398.7963679920012</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21611,28 +21722,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2726864014238115</v>
+        <v>-0.2767119125679923</v>
       </c>
       <c r="J6" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="K6" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07296435188738981</v>
+        <v>0.075627066569116</v>
       </c>
       <c r="M6" t="n">
-        <v>5.866065226698774</v>
+        <v>5.850437448828453</v>
       </c>
       <c r="N6" t="n">
-        <v>55.41958296892471</v>
+        <v>55.20021101092598</v>
       </c>
       <c r="O6" t="n">
-        <v>7.444433018633771</v>
+        <v>7.429684448947074</v>
       </c>
       <c r="P6" t="n">
-        <v>407.9159454859701</v>
+        <v>407.9565034252373</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21670,7 +21781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G538"/>
+  <dimension ref="A1:G541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41579,6 +41690,117 @@
         </is>
       </c>
     </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-35.012650219349844,173.8525861670102</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-35.01305574312712,173.85330264498484</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-35.01328235185681,173.85413730361887</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-35.01353826009713,173.85487890621653</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-35.013433761965594,173.85567589921</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-35.0126482952933,173.85258798001743</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>-35.01305451471467,173.85330356451976</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>-35.01328218776653,173.85413739453688</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-35.01353353961019,173.8548798114435</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-35.01342559614775,173.85567492278108</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-35.01265820062122,173.85257864638672</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>-35.01306342070477,173.85329689789094</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>-35.013290802505864,173.85413262134168</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-35.01354226805773,173.85487813762748</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-35.01343959469261,173.85567659665935</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G541"/>
+  <dimension ref="A1:G542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15043,6 +15043,33 @@
         <v>396.03</v>
       </c>
       <c r="G541" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>373.47</v>
+      </c>
+      <c r="C542" t="n">
+        <v>377.88</v>
+      </c>
+      <c r="D542" t="n">
+        <v>388.09</v>
+      </c>
+      <c r="E542" t="n">
+        <v>391.93</v>
+      </c>
+      <c r="F542" t="n">
+        <v>397.13</v>
+      </c>
+      <c r="G542" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15059,7 +15086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B618"/>
+  <dimension ref="A1:B619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21242,6 +21269,16 @@
       </c>
       <c r="B618" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -21410,28 +21447,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.16555759085466</v>
+        <v>0.1623449369527953</v>
       </c>
       <c r="J2" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K2" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1121122705547676</v>
+        <v>0.1073838912079909</v>
       </c>
       <c r="M2" t="n">
-        <v>2.760866761042239</v>
+        <v>2.771919950651437</v>
       </c>
       <c r="N2" t="n">
-        <v>12.80318917506866</v>
+        <v>12.94523713655123</v>
       </c>
       <c r="O2" t="n">
-        <v>3.57815443700641</v>
+        <v>3.597949018058931</v>
       </c>
       <c r="P2" t="n">
-        <v>378.590869402714</v>
+        <v>378.6233692787465</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21488,28 +21525,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2236478662760924</v>
+        <v>0.2204378009868649</v>
       </c>
       <c r="J3" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K3" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2145226629122596</v>
+        <v>0.2077823099122935</v>
       </c>
       <c r="M3" t="n">
-        <v>2.669573813277388</v>
+        <v>2.68318765907861</v>
       </c>
       <c r="N3" t="n">
-        <v>10.80202202755234</v>
+        <v>10.94750206225374</v>
       </c>
       <c r="O3" t="n">
-        <v>3.286642972327896</v>
+        <v>3.308700962954153</v>
       </c>
       <c r="P3" t="n">
-        <v>381.4641958199472</v>
+        <v>381.4966695090351</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21566,28 +21603,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03753634809745329</v>
+        <v>0.03544886067512599</v>
       </c>
       <c r="J4" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K4" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009929114832593733</v>
+        <v>0.008823341050690825</v>
       </c>
       <c r="M4" t="n">
-        <v>2.232058202294005</v>
+        <v>2.239906186030679</v>
       </c>
       <c r="N4" t="n">
-        <v>8.286570935819514</v>
+        <v>8.341218403909686</v>
       </c>
       <c r="O4" t="n">
-        <v>2.878640466577845</v>
+        <v>2.888116757319497</v>
       </c>
       <c r="P4" t="n">
-        <v>393.2727349051239</v>
+        <v>393.2938523626893</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21644,28 +21681,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04080745370151635</v>
+        <v>-0.04276597559767115</v>
       </c>
       <c r="J5" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K5" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01177772133284005</v>
+        <v>0.01287222830662071</v>
       </c>
       <c r="M5" t="n">
-        <v>2.319733521613529</v>
+        <v>2.326251399257127</v>
       </c>
       <c r="N5" t="n">
-        <v>8.241142422964277</v>
+        <v>8.287496039763868</v>
       </c>
       <c r="O5" t="n">
-        <v>2.870739002933613</v>
+        <v>2.878801146269722</v>
       </c>
       <c r="P5" t="n">
-        <v>398.7963679920012</v>
+        <v>398.8161808074417</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21722,28 +21759,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2767119125679923</v>
+        <v>-0.2779053174710778</v>
       </c>
       <c r="J6" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K6" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L6" t="n">
-        <v>0.075627066569116</v>
+        <v>0.07646075176596767</v>
       </c>
       <c r="M6" t="n">
-        <v>5.850437448828453</v>
+        <v>5.844671121769577</v>
       </c>
       <c r="N6" t="n">
-        <v>55.20021101092598</v>
+        <v>55.12104419616134</v>
       </c>
       <c r="O6" t="n">
-        <v>7.429684448947074</v>
+        <v>7.424354799991804</v>
       </c>
       <c r="P6" t="n">
-        <v>407.9565034252373</v>
+        <v>407.9685761578103</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21781,7 +21818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G541"/>
+  <dimension ref="A1:G542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41801,6 +41838,43 @@
         </is>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-35.01266461414252,173.8525726030275</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-35.01307409253724,173.85328890942867</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-35.013302452914964,173.8541261661619</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-35.013544672834115,173.85487767647402</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-35.01342972392379,173.8556754163605</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G542"/>
+  <dimension ref="A1:G543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15070,6 +15070,33 @@
         <v>397.13</v>
       </c>
       <c r="G542" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="C543" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="D543" t="n">
+        <v>387.75</v>
+      </c>
+      <c r="E543" t="n">
+        <v>394.03</v>
+      </c>
+      <c r="F543" t="n">
+        <v>404.17</v>
+      </c>
+      <c r="G543" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15086,7 +15113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B619"/>
+  <dimension ref="A1:B620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21279,6 +21306,16 @@
       </c>
       <c r="B619" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -21447,28 +21484,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1623449369527953</v>
+        <v>0.1596257624802096</v>
       </c>
       <c r="J2" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K2" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1073838912079909</v>
+        <v>0.1036917900091867</v>
       </c>
       <c r="M2" t="n">
-        <v>2.771919950651437</v>
+        <v>2.780411131368763</v>
       </c>
       <c r="N2" t="n">
-        <v>12.94523713655123</v>
+        <v>13.03883903365849</v>
       </c>
       <c r="O2" t="n">
-        <v>3.597949018058931</v>
+        <v>3.610933263528764</v>
       </c>
       <c r="P2" t="n">
-        <v>378.6233692787465</v>
+        <v>378.6510222154419</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21525,28 +21562,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2204378009868649</v>
+        <v>0.2175389533890235</v>
       </c>
       <c r="J3" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K3" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2077823099122935</v>
+        <v>0.2020957297669981</v>
       </c>
       <c r="M3" t="n">
-        <v>2.68318765907861</v>
+        <v>2.695233772712406</v>
       </c>
       <c r="N3" t="n">
-        <v>10.94750206225374</v>
+        <v>11.06082887683543</v>
       </c>
       <c r="O3" t="n">
-        <v>3.308700962954153</v>
+        <v>3.325782445806615</v>
       </c>
       <c r="P3" t="n">
-        <v>381.4966695090351</v>
+        <v>381.5261496508652</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21603,28 +21640,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03544886067512599</v>
+        <v>0.03324666827826225</v>
       </c>
       <c r="J4" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K4" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008823341050690825</v>
+        <v>0.007727139811752659</v>
       </c>
       <c r="M4" t="n">
-        <v>2.239906186030679</v>
+        <v>2.248287492743764</v>
       </c>
       <c r="N4" t="n">
-        <v>8.341218403909686</v>
+        <v>8.402887610107674</v>
       </c>
       <c r="O4" t="n">
-        <v>2.888116757319497</v>
+        <v>2.89877346650401</v>
       </c>
       <c r="P4" t="n">
-        <v>393.2938523626893</v>
+        <v>393.3162477946689</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21681,28 +21718,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04276597559767115</v>
+        <v>-0.04400654573007277</v>
       </c>
       <c r="J5" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K5" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01287222830662071</v>
+        <v>0.01362985238971193</v>
       </c>
       <c r="M5" t="n">
-        <v>2.326251399257127</v>
+        <v>2.328780177072975</v>
       </c>
       <c r="N5" t="n">
-        <v>8.287496039763868</v>
+        <v>8.296659741975862</v>
       </c>
       <c r="O5" t="n">
-        <v>2.878801146269722</v>
+        <v>2.880392289598044</v>
       </c>
       <c r="P5" t="n">
-        <v>398.8161808074417</v>
+        <v>398.8287969185752</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21759,28 +21796,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2779053174710778</v>
+        <v>-0.2766936018566287</v>
       </c>
       <c r="J6" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K6" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07646075176596767</v>
+        <v>0.07607717075666609</v>
       </c>
       <c r="M6" t="n">
-        <v>5.844671121769577</v>
+        <v>5.841913436071978</v>
       </c>
       <c r="N6" t="n">
-        <v>55.12104419616134</v>
+        <v>55.04267479905421</v>
       </c>
       <c r="O6" t="n">
-        <v>7.424354799991804</v>
+        <v>7.419075063581323</v>
       </c>
       <c r="P6" t="n">
-        <v>407.9685761578103</v>
+        <v>407.9562534857945</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21818,7 +21855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G542"/>
+  <dimension ref="A1:G543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41875,6 +41912,43 @@
         </is>
       </c>
     </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-35.01265428124695,173.85258233955022</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-35.01306695239039,173.8532942542274</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-35.01330524244948,173.85412462055518</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-35.0135259690179,173.85488126322247</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-35.013366551002676,173.85566786245514</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G543"/>
+  <dimension ref="A1:G545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15099,6 +15099,60 @@
       <c r="G543" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="C544" t="n">
+        <v>379.78</v>
+      </c>
+      <c r="D544" t="n">
+        <v>388.91</v>
+      </c>
+      <c r="E544" t="n">
+        <v>394.98</v>
+      </c>
+      <c r="F544" t="n">
+        <v>404.8</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>375.98</v>
+      </c>
+      <c r="C545" t="n">
+        <v>380.08</v>
+      </c>
+      <c r="D545" t="n">
+        <v>389.06</v>
+      </c>
+      <c r="E545" t="n">
+        <v>394.79</v>
+      </c>
+      <c r="F545" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B620"/>
+  <dimension ref="A1:B622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21316,6 +21370,26 @@
       </c>
       <c r="B620" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -21484,28 +21558,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1596257624802096</v>
+        <v>0.1547394484826545</v>
       </c>
       <c r="J2" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K2" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1036917900091867</v>
+        <v>0.09741664120379379</v>
       </c>
       <c r="M2" t="n">
-        <v>2.780411131368763</v>
+        <v>2.794579450961926</v>
       </c>
       <c r="N2" t="n">
-        <v>13.03883903365849</v>
+        <v>13.18229856787784</v>
       </c>
       <c r="O2" t="n">
-        <v>3.610933263528764</v>
+        <v>3.630743528242919</v>
       </c>
       <c r="P2" t="n">
-        <v>378.6510222154419</v>
+        <v>378.7007957339577</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21562,28 +21636,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2175389533890235</v>
+        <v>0.212571104556153</v>
       </c>
       <c r="J3" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K3" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2020957297669981</v>
+        <v>0.1931283755917912</v>
       </c>
       <c r="M3" t="n">
-        <v>2.695233772712406</v>
+        <v>2.715146796233534</v>
       </c>
       <c r="N3" t="n">
-        <v>11.06082887683543</v>
+        <v>11.21764514641579</v>
       </c>
       <c r="O3" t="n">
-        <v>3.325782445806615</v>
+        <v>3.349275316604443</v>
       </c>
       <c r="P3" t="n">
-        <v>381.5261496508652</v>
+        <v>381.576754506654</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21640,28 +21714,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03324666827826225</v>
+        <v>0.02973171926984941</v>
       </c>
       <c r="J4" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K4" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007727139811752659</v>
+        <v>0.00616259913542716</v>
       </c>
       <c r="M4" t="n">
-        <v>2.248287492743764</v>
+        <v>2.259944680571991</v>
       </c>
       <c r="N4" t="n">
-        <v>8.402887610107674</v>
+        <v>8.470837467144493</v>
       </c>
       <c r="O4" t="n">
-        <v>2.89877346650401</v>
+        <v>2.910470317172895</v>
       </c>
       <c r="P4" t="n">
-        <v>393.3162477946689</v>
+        <v>393.3520528339232</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21718,28 +21792,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04400654573007277</v>
+        <v>-0.04587815077762872</v>
       </c>
       <c r="J5" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K5" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01362985238971193</v>
+        <v>0.01485498437928356</v>
       </c>
       <c r="M5" t="n">
-        <v>2.328780177072975</v>
+        <v>2.33044765494167</v>
       </c>
       <c r="N5" t="n">
-        <v>8.296659741975862</v>
+        <v>8.294202947718471</v>
       </c>
       <c r="O5" t="n">
-        <v>2.880392289598044</v>
+        <v>2.879965789331268</v>
       </c>
       <c r="P5" t="n">
-        <v>398.8287969185752</v>
+        <v>398.8478625842866</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21796,28 +21870,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2766936018566287</v>
+        <v>-0.2738197843952054</v>
       </c>
       <c r="J6" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K6" t="n">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07607717075666609</v>
+        <v>0.07505147279365465</v>
       </c>
       <c r="M6" t="n">
-        <v>5.841913436071978</v>
+        <v>5.839511395343666</v>
       </c>
       <c r="N6" t="n">
-        <v>55.04267479905421</v>
+        <v>54.90638847602543</v>
       </c>
       <c r="O6" t="n">
-        <v>7.419075063581323</v>
+        <v>7.409884511652353</v>
       </c>
       <c r="P6" t="n">
-        <v>407.9562534857945</v>
+        <v>407.9269787344221</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21855,7 +21929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G543"/>
+  <dimension ref="A1:G545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41949,6 +42023,80 @@
         </is>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-35.012651573315566,173.85258489119028</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-35.01305950514019,173.85329982890897</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-35.01329572521399,173.85412989380114</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-35.01351750776765,173.85488288579865</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-35.01336089774406,173.85566718646706</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-35.012646727543505,173.85258945728253</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-35.013057201866886,173.85330155303708</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-35.01329449453696,173.85413057568633</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-35.0135192000177,173.8548825612834</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-35.01335955173008,173.85566702551753</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G545"/>
+  <dimension ref="A1:G549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15153,6 +15153,114 @@
       <c r="G545" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>374.72</v>
+      </c>
+      <c r="C546" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="D546" t="n">
+        <v>388.55</v>
+      </c>
+      <c r="E546" t="n">
+        <v>395.16</v>
+      </c>
+      <c r="F546" t="n">
+        <v>401.26</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="C547" t="n">
+        <v>380</v>
+      </c>
+      <c r="D547" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="E547" t="n">
+        <v>395.54</v>
+      </c>
+      <c r="F547" t="n">
+        <v>397.14</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>375.25</v>
+      </c>
+      <c r="C548" t="n">
+        <v>380.71</v>
+      </c>
+      <c r="D548" t="n">
+        <v>389.22</v>
+      </c>
+      <c r="E548" t="n">
+        <v>395.62</v>
+      </c>
+      <c r="F548" t="n">
+        <v>396.55</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>375.98</v>
+      </c>
+      <c r="C549" t="n">
+        <v>380.82</v>
+      </c>
+      <c r="D549" t="n">
+        <v>389.54</v>
+      </c>
+      <c r="E549" t="n">
+        <v>395.23</v>
+      </c>
+      <c r="F549" t="n">
+        <v>397.31</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B622"/>
+  <dimension ref="A1:B626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21390,6 +21498,46 @@
       </c>
       <c r="B622" t="n">
         <v>0.93</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -21558,28 +21706,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1547394484826545</v>
+        <v>0.1445434591161216</v>
       </c>
       <c r="J2" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K2" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09741664120379379</v>
+        <v>0.08475868507536943</v>
       </c>
       <c r="M2" t="n">
-        <v>2.794579450961926</v>
+        <v>2.826464257665817</v>
       </c>
       <c r="N2" t="n">
-        <v>13.18229856787784</v>
+        <v>13.50587310209078</v>
       </c>
       <c r="O2" t="n">
-        <v>3.630743528242919</v>
+        <v>3.675033755231479</v>
       </c>
       <c r="P2" t="n">
-        <v>378.7007957339577</v>
+        <v>378.8052290379057</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21636,28 +21784,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.212571104556153</v>
+        <v>0.203282596976159</v>
       </c>
       <c r="J3" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K3" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1931283755917912</v>
+        <v>0.1772304815008782</v>
       </c>
       <c r="M3" t="n">
-        <v>2.715146796233534</v>
+        <v>2.751094583904585</v>
       </c>
       <c r="N3" t="n">
-        <v>11.21764514641579</v>
+        <v>11.48456495904141</v>
       </c>
       <c r="O3" t="n">
-        <v>3.349275316604443</v>
+        <v>3.388888454794789</v>
       </c>
       <c r="P3" t="n">
-        <v>381.576754506654</v>
+        <v>381.6718911563841</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21714,28 +21862,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02973171926984941</v>
+        <v>0.02284267229505973</v>
       </c>
       <c r="J4" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K4" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00616259913542716</v>
+        <v>0.003618606807826219</v>
       </c>
       <c r="M4" t="n">
-        <v>2.259944680571991</v>
+        <v>2.282979732585906</v>
       </c>
       <c r="N4" t="n">
-        <v>8.470837467144493</v>
+        <v>8.601068433246837</v>
       </c>
       <c r="O4" t="n">
-        <v>2.910470317172895</v>
+        <v>2.932757820422074</v>
       </c>
       <c r="P4" t="n">
-        <v>393.3520528339232</v>
+        <v>393.4226134724537</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21792,28 +21940,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04587815077762872</v>
+        <v>-0.04885906204414906</v>
       </c>
       <c r="J5" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K5" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01485498437928356</v>
+        <v>0.01698775346243908</v>
       </c>
       <c r="M5" t="n">
-        <v>2.33044765494167</v>
+        <v>2.329577196930012</v>
       </c>
       <c r="N5" t="n">
-        <v>8.294202947718471</v>
+        <v>8.269658991748086</v>
       </c>
       <c r="O5" t="n">
-        <v>2.879965789331268</v>
+        <v>2.875701478204594</v>
       </c>
       <c r="P5" t="n">
-        <v>398.8478625842866</v>
+        <v>398.8783954498542</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21870,28 +22018,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2738197843952054</v>
+        <v>-0.2772392034107469</v>
       </c>
       <c r="J6" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="K6" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07505147279365465</v>
+        <v>0.07775273820685169</v>
       </c>
       <c r="M6" t="n">
-        <v>5.839511395343666</v>
+        <v>5.813672717479628</v>
       </c>
       <c r="N6" t="n">
-        <v>54.90638847602543</v>
+        <v>54.57771362380801</v>
       </c>
       <c r="O6" t="n">
-        <v>7.409884511652353</v>
+        <v>7.387673085878125</v>
       </c>
       <c r="P6" t="n">
-        <v>407.9269787344221</v>
+        <v>407.9620312335675</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21929,7 +22077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G545"/>
+  <dimension ref="A1:G549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42097,6 +42245,154 @@
         </is>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-35.012655706473964,173.8525809965817</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-35.01306127098304,173.85329850707734</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-35.013298678838815,173.85412825727667</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-35.0135159045834,173.8548831932341</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-35.01339266367335,173.85567098487755</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-35.012655492689916,173.852581198027</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-35.013057816073115,173.8533010932696</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-35.01329826861315,173.85412848457176</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-35.01351252008329,173.85488384226443</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-35.013429634189535,173.8556754056305</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-35.01265192962233,173.85258455544817</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-35.01305236499287,173.85330517370582</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-35.013293181814795,173.85413130303047</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-35.01351180755695,173.85488397890242</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-35.01343492851101,173.85567603869987</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-35.012646727543505,173.85258945728253</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-35.0130515204593,173.85330580588604</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-35.013290556370464,173.8541327577187</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-35.01351528112285,173.8548833127923</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-35.01342810870709,173.85567522322071</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G549"/>
+  <dimension ref="A1:G552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15259,6 +15259,87 @@
         <v>397.31</v>
       </c>
       <c r="G549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>375.37</v>
+      </c>
+      <c r="C550" t="n">
+        <v>380.25</v>
+      </c>
+      <c r="D550" t="n">
+        <v>389.75</v>
+      </c>
+      <c r="E550" t="n">
+        <v>395.09</v>
+      </c>
+      <c r="F550" t="n">
+        <v>396.71</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>374.95</v>
+      </c>
+      <c r="C551" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="D551" t="n">
+        <v>389.41</v>
+      </c>
+      <c r="E551" t="n">
+        <v>394.4</v>
+      </c>
+      <c r="F551" t="n">
+        <v>395.69</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>376.04</v>
+      </c>
+      <c r="C552" t="n">
+        <v>380.39</v>
+      </c>
+      <c r="D552" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="E552" t="n">
+        <v>395.12</v>
+      </c>
+      <c r="F552" t="n">
+        <v>396.16</v>
+      </c>
+      <c r="G552" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15275,7 +15356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B626"/>
+  <dimension ref="A1:B629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21538,6 +21619,36 @@
       </c>
       <c r="B626" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -21706,28 +21817,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1445434591161216</v>
+        <v>0.1374022711962281</v>
       </c>
       <c r="J2" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K2" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08475868507536943</v>
+        <v>0.07653499600979252</v>
       </c>
       <c r="M2" t="n">
-        <v>2.826464257665817</v>
+        <v>2.847987436201825</v>
       </c>
       <c r="N2" t="n">
-        <v>13.50587310209078</v>
+        <v>13.71221918676662</v>
       </c>
       <c r="O2" t="n">
-        <v>3.675033755231479</v>
+        <v>3.703001375474579</v>
       </c>
       <c r="P2" t="n">
-        <v>378.8052290379057</v>
+        <v>378.8786322777508</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21784,28 +21895,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.203282596976159</v>
+        <v>0.1965816017102689</v>
       </c>
       <c r="J3" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K3" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1772304815008782</v>
+        <v>0.1662311543185505</v>
       </c>
       <c r="M3" t="n">
-        <v>2.751094583904585</v>
+        <v>2.777197062036785</v>
       </c>
       <c r="N3" t="n">
-        <v>11.48456495904141</v>
+        <v>11.66751927805562</v>
       </c>
       <c r="O3" t="n">
-        <v>3.388888454794789</v>
+        <v>3.41577506256715</v>
       </c>
       <c r="P3" t="n">
-        <v>381.6718911563841</v>
+        <v>381.7407715070852</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21862,28 +21973,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02284267229505973</v>
+        <v>0.01852226117488765</v>
       </c>
       <c r="J4" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K4" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003618606807826219</v>
+        <v>0.00237997290809655</v>
       </c>
       <c r="M4" t="n">
-        <v>2.282979732585906</v>
+        <v>2.295763483430996</v>
       </c>
       <c r="N4" t="n">
-        <v>8.601068433246837</v>
+        <v>8.6564674196936</v>
       </c>
       <c r="O4" t="n">
-        <v>2.932757820422074</v>
+        <v>2.94218752286349</v>
       </c>
       <c r="P4" t="n">
-        <v>393.4226134724537</v>
+        <v>393.4670235100144</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21940,28 +22051,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04885906204414906</v>
+        <v>-0.05153440120291939</v>
       </c>
       <c r="J5" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K5" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01698775346243908</v>
+        <v>0.01897683656287319</v>
       </c>
       <c r="M5" t="n">
-        <v>2.329577196930012</v>
+        <v>2.331344366360366</v>
       </c>
       <c r="N5" t="n">
-        <v>8.269658991748086</v>
+        <v>8.264364409566715</v>
       </c>
       <c r="O5" t="n">
-        <v>2.875701478204594</v>
+        <v>2.87478075852172</v>
       </c>
       <c r="P5" t="n">
-        <v>398.8783954498542</v>
+        <v>398.9058957754602</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22018,28 +22129,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2772392034107469</v>
+        <v>-0.2815620749343369</v>
       </c>
       <c r="J6" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K6" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07775273820685169</v>
+        <v>0.08066985376371894</v>
       </c>
       <c r="M6" t="n">
-        <v>5.813672717479628</v>
+        <v>5.800592661320131</v>
       </c>
       <c r="N6" t="n">
-        <v>54.57771362380801</v>
+        <v>54.38361737534532</v>
       </c>
       <c r="O6" t="n">
-        <v>7.387673085878125</v>
+        <v>7.374524891499473</v>
       </c>
       <c r="P6" t="n">
-        <v>407.9620312335675</v>
+        <v>408.0064690449678</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22077,7 +22188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G549"/>
+  <dimension ref="A1:G552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42393,6 +42504,117 @@
         </is>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-35.01265107448611,173.8525853612292</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-35.01305589667867,173.85330253004298</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-35.013288833422614,173.85413371235782</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-35.013516528043944,173.85488307367586</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-35.0134334927628,173.85567586702</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-35.0126540674629,173.85258254099548</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-35.01305505214511,173.85330316222323</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-35.01329162295722,173.8541321667516</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-35.01352267358359,173.85488189517324</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-35.013442645657506,173.85567696147905</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-35.012646299975366,173.85258986017297</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-35.01305482181779,173.85330333463602</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-35.01328801297125,173.85413416694786</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-35.013516260846565,173.85488312491512</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-35.013438428147204,173.85567645716947</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0048/nzd0048.xlsx
+++ b/data/nzd0048/nzd0048.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G552"/>
+  <dimension ref="A1:G557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15340,6 +15340,141 @@
         <v>396.16</v>
       </c>
       <c r="G552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>375.88</v>
+      </c>
+      <c r="C553" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="D553" t="n">
+        <v>389.63</v>
+      </c>
+      <c r="E553" t="n">
+        <v>394.65</v>
+      </c>
+      <c r="F553" t="n">
+        <v>394.91</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="C554" t="n">
+        <v>380.17</v>
+      </c>
+      <c r="D554" t="n">
+        <v>390.61</v>
+      </c>
+      <c r="E554" t="n">
+        <v>394.67</v>
+      </c>
+      <c r="F554" t="n">
+        <v>392.59</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>376.89</v>
+      </c>
+      <c r="C555" t="n">
+        <v>380.91</v>
+      </c>
+      <c r="D555" t="n">
+        <v>391.52</v>
+      </c>
+      <c r="E555" t="n">
+        <v>395.87</v>
+      </c>
+      <c r="F555" t="n">
+        <v>392.95</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>378.17</v>
+      </c>
+      <c r="C556" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="D556" t="n">
+        <v>392.27</v>
+      </c>
+      <c r="E556" t="n">
+        <v>396.66</v>
+      </c>
+      <c r="F556" t="n">
+        <v>397.56</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>378.87</v>
+      </c>
+      <c r="C557" t="n">
+        <v>382.85</v>
+      </c>
+      <c r="D557" t="n">
+        <v>392.66</v>
+      </c>
+      <c r="E557" t="n">
+        <v>397.09</v>
+      </c>
+      <c r="F557" t="n">
+        <v>398.37</v>
+      </c>
+      <c r="G557" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15356,7 +15491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B629"/>
+  <dimension ref="A1:B634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21649,6 +21784,56 @@
       </c>
       <c r="B629" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -21817,28 +22002,28 @@
         <v>0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1374022711962281</v>
+        <v>0.1285894655068082</v>
       </c>
       <c r="J2" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="K2" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07653499600979252</v>
+        <v>0.06755790657053695</v>
       </c>
       <c r="M2" t="n">
-        <v>2.847987436201825</v>
+        <v>2.86857645928073</v>
       </c>
       <c r="N2" t="n">
-        <v>13.71221918676662</v>
+        <v>13.86190963442748</v>
       </c>
       <c r="O2" t="n">
-        <v>3.703001375474579</v>
+        <v>3.723158556176124</v>
       </c>
       <c r="P2" t="n">
-        <v>378.8786322777508</v>
+        <v>378.9696094479206</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21895,28 +22080,28 @@
         <v>0.0888</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1965816017102689</v>
+        <v>0.1871304657808862</v>
       </c>
       <c r="J3" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="K3" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1662311543185505</v>
+        <v>0.1519412248066331</v>
       </c>
       <c r="M3" t="n">
-        <v>2.777197062036785</v>
+        <v>2.810775115817306</v>
       </c>
       <c r="N3" t="n">
-        <v>11.66751927805562</v>
+        <v>11.87150884489777</v>
       </c>
       <c r="O3" t="n">
-        <v>3.41577506256715</v>
+        <v>3.445505600764243</v>
       </c>
       <c r="P3" t="n">
-        <v>381.7407715070852</v>
+        <v>381.838340915247</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21973,28 +22158,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01852226117488765</v>
+        <v>0.01427610179507694</v>
       </c>
       <c r="J4" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="K4" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00237997290809655</v>
+        <v>0.001429077525791578</v>
       </c>
       <c r="M4" t="n">
-        <v>2.295763483430996</v>
+        <v>2.299731232634274</v>
       </c>
       <c r="N4" t="n">
-        <v>8.6564674196936</v>
+        <v>8.649858282425472</v>
       </c>
       <c r="O4" t="n">
-        <v>2.94218752286349</v>
+        <v>2.941064141161405</v>
       </c>
       <c r="P4" t="n">
-        <v>393.4670235100144</v>
+        <v>393.5108507329039</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22051,28 +22236,28 @@
         <v>0.1137</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05153440120291939</v>
+        <v>-0.05434122901438122</v>
       </c>
       <c r="J5" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="K5" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01897683656287319</v>
+        <v>0.02134029440320839</v>
       </c>
       <c r="M5" t="n">
-        <v>2.331344366360366</v>
+        <v>2.325443213280896</v>
       </c>
       <c r="N5" t="n">
-        <v>8.264364409566715</v>
+        <v>8.225395851263745</v>
       </c>
       <c r="O5" t="n">
-        <v>2.87478075852172</v>
+        <v>2.867995092615004</v>
       </c>
       <c r="P5" t="n">
-        <v>398.9058957754602</v>
+        <v>398.9348640970946</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22129,28 +22314,28 @@
         <v>0.0476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2815620749343369</v>
+        <v>-0.2899414979298609</v>
       </c>
       <c r="J6" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="K6" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08066985376371894</v>
+        <v>0.0861277692920448</v>
       </c>
       <c r="M6" t="n">
-        <v>5.800592661320131</v>
+        <v>5.784407516257978</v>
       </c>
       <c r="N6" t="n">
-        <v>54.38361737534532</v>
+        <v>54.17883125241834</v>
       </c>
       <c r="O6" t="n">
-        <v>7.374524891499473</v>
+        <v>7.360627096410899</v>
       </c>
       <c r="P6" t="n">
-        <v>408.0064690449678</v>
+        <v>408.0929653061941</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22188,7 +22373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G552"/>
+  <dimension ref="A1:G557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42615,6 +42800,191 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-35.01264744015703,173.85258878579842</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-35.01305789284888,173.85330103579867</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-35.01328981796424,173.85413316684978</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-35.013520446938784,173.85488232216696</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-35.01344964492991,173.85567779841853</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-35.012648152770595,173.85258811431424</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-35.01305651088489,173.8533020702755</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-35.013281777540854,173.85413762183185</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-35.01352026880721,173.85488235632644</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-35.0134704632785,173.85568028777777</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-35.012640242760014,173.85259556778752</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-35.013050829477294,173.85330632312437</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-35.01327431143326,173.85414175860018</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-35.01350958091215,173.85488440589603</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-35.01346723284511,173.8556799014978</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-35.01263112130582,173.85260416278192</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-35.01304292157186,173.85331224262927</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-35.0132681580478,173.85414516802402</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-35.013502544714534,173.8548857551957</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-35.013425865350534,173.85567495497102</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-35.012626133010315,173.85260886316868</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-35.013035934975555,173.85331747248216</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-35.01326495828731,173.85414694092424</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-35.01349871488544,173.85488648962456</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-35.01341859687528,173.85567408584217</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
